--- a/algorithm/output_result/return_metrics/TATA AIA nav_Return_Metrics.xlsx
+++ b/algorithm/output_result/return_metrics/TATA AIA nav_Return_Metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,31 @@
           <t>1Y Return (%)</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Average Return</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Broad Category</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Return Rank</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Funds in Category</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Return Score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +506,23 @@
       <c r="G2" t="n">
         <v>3.98</v>
       </c>
+      <c r="H2" t="n">
+        <v>2.7775</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>38.89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,6 +552,23 @@
       <c r="G3" t="n">
         <v>2.88</v>
       </c>
+      <c r="H3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,6 +598,23 @@
       <c r="G4" t="n">
         <v>3.75</v>
       </c>
+      <c r="H4" t="n">
+        <v>2.5475</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -568,6 +644,23 @@
       <c r="G5" t="n">
         <v>5.26</v>
       </c>
+      <c r="H5" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -597,6 +690,23 @@
       <c r="G6" t="n">
         <v>3.53</v>
       </c>
+      <c r="H6" t="n">
+        <v>4.697500000000001</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>19</v>
+      </c>
+      <c r="L6" t="n">
+        <v>72.22</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -626,6 +736,23 @@
       <c r="G7" t="n">
         <v>1.94</v>
       </c>
+      <c r="H7" t="n">
+        <v>3.635</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" t="n">
+        <v>44.44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -655,6 +782,23 @@
       <c r="G8" t="n">
         <v>4.2</v>
       </c>
+      <c r="H8" t="n">
+        <v>4.5275</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L8" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -684,6 +828,23 @@
       <c r="G9" t="n">
         <v>9.529999999999999</v>
       </c>
+      <c r="H9" t="n">
+        <v>8.105</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19</v>
+      </c>
+      <c r="L9" t="n">
+        <v>94.44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -713,6 +874,23 @@
       <c r="G10" t="n">
         <v>4.66</v>
       </c>
+      <c r="H10" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>61.11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -742,6 +920,23 @@
       <c r="G11" t="n">
         <v>12.14</v>
       </c>
+      <c r="H11" t="n">
+        <v>10.285</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19</v>
+      </c>
+      <c r="L11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -771,6 +966,23 @@
       <c r="G12" t="n">
         <v>6.49</v>
       </c>
+      <c r="H12" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L12" t="n">
+        <v>77.78</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -800,6 +1012,23 @@
       <c r="G13" t="n">
         <v>-0.5</v>
       </c>
+      <c r="H13" t="n">
+        <v>0.8275000000000001</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" t="n">
+        <v>19</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22.22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -829,6 +1058,23 @@
       <c r="G14" t="n">
         <v>-3.52</v>
       </c>
+      <c r="H14" t="n">
+        <v>-1.075</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -858,6 +1104,23 @@
       <c r="G15" t="n">
         <v>3.01</v>
       </c>
+      <c r="H15" t="n">
+        <v>3.9625</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>19</v>
+      </c>
+      <c r="L15" t="n">
+        <v>55.56</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -885,6 +1148,23 @@
         <v>7.66</v>
       </c>
       <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>3.763333333333333</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>19</v>
+      </c>
+      <c r="L16" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -914,6 +1194,23 @@
       <c r="G17" t="n">
         <v>-0.35</v>
       </c>
+      <c r="H17" t="n">
+        <v>1.7425</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K17" t="n">
+        <v>19</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -943,6 +1240,23 @@
       <c r="G18" t="n">
         <v>6.23</v>
       </c>
+      <c r="H18" t="n">
+        <v>5.6825</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>19</v>
+      </c>
+      <c r="L18" t="n">
+        <v>88.89</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -972,6 +1286,23 @@
       <c r="G19" t="n">
         <v>2.35</v>
       </c>
+      <c r="H19" t="n">
+        <v>5.3775</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" t="n">
+        <v>83.33</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -999,6 +1330,23 @@
         <v>0.46</v>
       </c>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.6533333333333333</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.56</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1028,6 +1376,23 @@
       <c r="G21" t="n">
         <v>1.27</v>
       </c>
+      <c r="H21" t="n">
+        <v>0.7525000000000001</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>17</v>
+      </c>
+      <c r="K21" t="n">
+        <v>19</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11.11</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1057,6 +1422,23 @@
       <c r="G22" t="n">
         <v>0.92</v>
       </c>
+      <c r="H22" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>19</v>
+      </c>
+      <c r="L22" t="n">
+        <v>16.67</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1085,6 +1467,23 @@
       </c>
       <c r="G23" t="n">
         <v>0.67</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" t="n">
+        <v>19</v>
+      </c>
+      <c r="L23" t="n">
+        <v>27.78</v>
       </c>
     </row>
   </sheetData>

--- a/algorithm/output_result/return_metrics/TATA AIA nav_Return_Metrics.xlsx
+++ b/algorithm/output_result/return_metrics/TATA AIA nav_Return_Metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,19 +495,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="E2" t="n">
-        <v>2.46</v>
+        <v>4.02</v>
       </c>
       <c r="F2" t="n">
-        <v>3.79</v>
+        <v>3.53</v>
       </c>
       <c r="G2" t="n">
-        <v>3.98</v>
+        <v>5.77</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7775</v>
+        <v>3.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>38.89</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="3">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="n">
-        <v>2.07</v>
+        <v>3.39</v>
       </c>
       <c r="F3" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>4.23</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>2.8575</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.87</v>
+        <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="F4" t="n">
-        <v>3.36</v>
+        <v>3.09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.75</v>
+        <v>4.04</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5475</v>
+        <v>2.42</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="E5" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="F5" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
-        <v>5.26</v>
+        <v>5.33</v>
       </c>
       <c r="H5" t="n">
-        <v>2.545</v>
+        <v>2.5925</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4</v>
+        <v>7.12</v>
       </c>
       <c r="F6" t="n">
-        <v>7.36</v>
+        <v>6.11</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53</v>
+        <v>5.32</v>
       </c>
       <c r="H6" t="n">
-        <v>4.697500000000001</v>
+        <v>5.365</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>72.22</v>
+        <v>64.70999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.85</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3.84</v>
+        <v>6.5</v>
       </c>
       <c r="F7" t="n">
-        <v>7.91</v>
+        <v>5.62</v>
       </c>
       <c r="G7" t="n">
-        <v>1.94</v>
+        <v>3.04</v>
       </c>
       <c r="H7" t="n">
-        <v>3.635</v>
+        <v>4.54</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L7" t="n">
-        <v>44.44</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="8">
@@ -762,28 +762,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Multi Cap Fund</t>
+          <t>Emerging Opportunities Fund</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ULIF 060 15/07/14 MCF 110</t>
+          <t>ULIF 064 12/09/22 EOF 110</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.62</v>
+        <v>4.55</v>
       </c>
       <c r="E8" t="n">
-        <v>4.16</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>8.130000000000001</v>
+        <v>10.95</v>
       </c>
       <c r="G8" t="n">
-        <v>4.2</v>
+        <v>12.57</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5275</v>
+        <v>9.297499999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L8" t="n">
-        <v>66.67</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="9">
@@ -808,28 +808,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emerging Opportunities Fund</t>
+          <t>Flexi Growth Fund</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ULIF 064 12/09/22 EOF 110</t>
+          <t>ULIF 068 25/04/23 FGF 110</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.88</v>
+        <v>3.29</v>
       </c>
       <c r="E9" t="n">
-        <v>7.6</v>
+        <v>6.85</v>
       </c>
       <c r="F9" t="n">
-        <v>12.41</v>
+        <v>6.98</v>
       </c>
       <c r="G9" t="n">
-        <v>9.529999999999999</v>
+        <v>6.89</v>
       </c>
       <c r="H9" t="n">
-        <v>8.105</v>
+        <v>6.0025</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
-        <v>94.44</v>
+        <v>76.47</v>
       </c>
     </row>
     <row r="10">
@@ -854,28 +854,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Flexi Growth Fund</t>
+          <t>Small Cap Discovery Fund</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ULIF 068 25/04/23 FGF 110</t>
+          <t>ULIF 071 22/05/23 SCF 110</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.63</v>
+        <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>3.66</v>
+        <v>9.01</v>
       </c>
       <c r="F10" t="n">
-        <v>7.71</v>
+        <v>13.85</v>
       </c>
       <c r="G10" t="n">
-        <v>4.66</v>
+        <v>15.88</v>
       </c>
       <c r="H10" t="n">
-        <v>4.415</v>
+        <v>10.515</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L10" t="n">
-        <v>61.11</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -900,28 +900,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Small Cap Discovery Fund</t>
+          <t>Rising India Fund</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ULIF 071 22/05/23 SCF 110</t>
+          <t>ULIF 073 17/01/24 RIF 110</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="E11" t="n">
-        <v>8.550000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="F11" t="n">
-        <v>17.16</v>
+        <v>6.47</v>
       </c>
       <c r="G11" t="n">
-        <v>12.14</v>
+        <v>8.76</v>
       </c>
       <c r="H11" t="n">
-        <v>10.285</v>
+        <v>6.529999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -946,28 +946,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rising India Fund</t>
+          <t>Midcap Momentum Index Fund</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ULIF 073 17/01/24 RIF 110</t>
+          <t>ULIF 075 09/05/24 MIF 110</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.6</v>
+        <v>-0.47</v>
       </c>
       <c r="E12" t="n">
-        <v>5.37</v>
+        <v>2.78</v>
       </c>
       <c r="F12" t="n">
-        <v>6.98</v>
+        <v>3.46</v>
       </c>
       <c r="G12" t="n">
-        <v>6.49</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="n">
-        <v>5.11</v>
+        <v>1.815</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>77.78</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="13">
@@ -992,28 +992,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Midcap Momentum Index Fund</t>
+          <t>Multicap Momentum Quality Index Fund</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ULIF 075 09/05/24 MIF 110</t>
+          <t>ULIF 078 31/12/24 MQI 110</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-2.51</v>
+        <v>-1.3</v>
       </c>
       <c r="E13" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.74</v>
       </c>
-      <c r="F13" t="n">
-        <v>5.58</v>
-      </c>
       <c r="G13" t="n">
-        <v>-0.5</v>
+        <v>-1.05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8275000000000001</v>
+        <v>-0.7425</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L13" t="n">
-        <v>22.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1038,28 +1038,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Multicap Momentum Quality Index Fund</t>
+          <t>Tax Bonanza Consumption Fund</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ULIF 078 31/12/24 MQI 110</t>
+          <t>ULIF 088 31/03/25 TBC 110</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-3.14</v>
+        <v>2.91</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.51</v>
+        <v>6.67</v>
       </c>
       <c r="F14" t="n">
-        <v>3.87</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.52</v>
+        <v>4.86</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.075</v>
+        <v>5.11</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="15">
@@ -1084,28 +1084,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tax Bonanza Consumption Fund</t>
+          <t>Momentum 50 Index Fund</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ULIF 088 31/03/25 TBC 110</t>
+          <t>ULIF 092 25/08/25 MFI 110</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.45</v>
+        <v>0.44</v>
       </c>
       <c r="E15" t="n">
-        <v>5.21</v>
+        <v>5.64</v>
       </c>
       <c r="F15" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3.01</v>
-      </c>
+        <v>6.15</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3.9625</v>
+        <v>4.076666666666667</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1113,13 +1111,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L15" t="n">
-        <v>55.56</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="16">
@@ -1130,26 +1128,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Momentum 50 Index Fund</t>
+          <t>Sustainable Equity Fund</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ULIF 092 25/08/25 MFI 110</t>
+          <t>ULIF 145 03/06/21 SustainEqu 105</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.29</v>
+        <v>3.18</v>
       </c>
       <c r="E16" t="n">
-        <v>3.92</v>
+        <v>5.78</v>
       </c>
       <c r="F16" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>3.16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.36</v>
+      </c>
       <c r="H16" t="n">
-        <v>3.763333333333333</v>
+        <v>3.62</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="17">
@@ -1174,28 +1174,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sustainable Equity Fund</t>
+          <t>India Consumption Fund</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ULIF 145 03/06/21 SustainEqu 105</t>
+          <t>ULIF 158 170425 IndConsump 105</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>3.87</v>
       </c>
       <c r="E17" t="n">
-        <v>2.73</v>
+        <v>7.39</v>
       </c>
       <c r="F17" t="n">
-        <v>3.09</v>
+        <v>8.49</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.35</v>
+        <v>8.92</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7425</v>
+        <v>7.1675</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L17" t="n">
-        <v>33.33</v>
+        <v>88.23999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1220,28 +1220,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>India Consumption Fund</t>
+          <t>Nifty Alpha 50 Index Fund</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ULIF 158 170425 IndConsump 105</t>
+          <t>ULIF 160 290725 AlphaIndIF 105</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.44</v>
+        <v>0.88</v>
       </c>
       <c r="E18" t="n">
-        <v>5.6</v>
+        <v>6.52</v>
       </c>
       <c r="F18" t="n">
-        <v>8.460000000000001</v>
+        <v>11.34</v>
       </c>
       <c r="G18" t="n">
-        <v>6.23</v>
+        <v>3.4</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6825</v>
+        <v>5.534999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>88.89</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="19">
@@ -1266,28 +1266,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nifty Alpha 50 Index Fund</t>
+          <t>Sector Leaders Index Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ULIF 160 290725 AlphaIndIF 105</t>
+          <t>ULIF 162 251125 SecLeaders 105</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>5.94</v>
+        <v>2.49</v>
       </c>
       <c r="F19" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.35</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>5.3775</v>
+        <v>1.973333333333333</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1295,13 +1293,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L19" t="n">
-        <v>83.33</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="20">
@@ -1312,26 +1310,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sector Leaders Index Fund</t>
+          <t>Large Cap Equity Fund</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ULIF 162 251125 SecLeaders 105</t>
+          <t>ULIF017 07/01/08 TLC 110</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.96</v>
+        <v>2.65</v>
       </c>
       <c r="E20" t="n">
-        <v>0.54</v>
+        <v>4.13</v>
       </c>
       <c r="F20" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>-0.19</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.23</v>
+      </c>
       <c r="H20" t="n">
-        <v>0.6533333333333333</v>
+        <v>2.455</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L20" t="n">
-        <v>5.56</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="21">
@@ -1356,28 +1356,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Large Cap Equity Fund</t>
+          <t>Top 50 Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ULIF017 07/01/08 TLC 110</t>
+          <t>ULIF026 12/01/09 ITF 110</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.31</v>
+        <v>2.58</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.17</v>
+        <v>0.3</v>
       </c>
       <c r="G21" t="n">
-        <v>1.27</v>
+        <v>2.89</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7525000000000001</v>
+        <v>2.5425</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L21" t="n">
-        <v>11.11</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="22">
@@ -1402,28 +1402,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Top 50 Fund</t>
+          <t>Dynamic Advantage Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ULIF026 12/01/09 ITF 110</t>
+          <t>ULIF08028/02/25DynamicFnd101</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="E22" t="n">
-        <v>0.78</v>
+        <v>3.58</v>
       </c>
       <c r="F22" t="n">
-        <v>0.15</v>
+        <v>1.48</v>
       </c>
       <c r="G22" t="n">
-        <v>0.92</v>
+        <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7775</v>
+        <v>2.1725</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1431,59 +1431,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L22" t="n">
-        <v>16.67</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TATA AIA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Dynamic Advantage Fund</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ULIF08028/02/25DynamicFnd101</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>14</v>
-      </c>
-      <c r="K23" t="n">
-        <v>19</v>
-      </c>
-      <c r="L23" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
     </row>
   </sheetData>
